--- a/output/anova_no_high_cooksd.xlsx
+++ b/output/anova_no_high_cooksd.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>221.3322329879559</v>
+        <v>985.8341015746004</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.817877852559517</v>
+        <v>6.192454502646537</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006337110630463313</v>
+        <v>0.01773652430311499</v>
       </c>
     </row>
     <row r="3">
@@ -476,35 +476,35 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2168.003373182135</v>
+        <v>6509.283804521312</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>86.37327094466791</v>
+        <v>40.88765415999554</v>
       </c>
       <c r="E3" t="n">
-        <v>9.525682039090606e-10</v>
+        <v>2.342819698597208e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Power (W) × Anneal Condition Num</t>
+          <t>Q('Power (W)'):C(Q('Anneal Condition Num'))</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8065312775149257</v>
+        <v>436.4319739530884</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03213221225569256</v>
+        <v>2.741419816871904</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8591274131896516</v>
+        <v>0.1067182923673091</v>
       </c>
     </row>
     <row r="5">
@@ -514,355 +514,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2411.825245829363</v>
+        <v>3717.920058929963</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>96.0871362130067</v>
+        <v>23.35387949415393</v>
       </c>
       <c r="E5" t="n">
-        <v>3.207142591276204e-10</v>
+        <v>2.657477552743092e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Substrate Temp (°C) × Anneal Condition Num</t>
+          <t>O2 Flow (sccm)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>143.5321392795687</v>
+        <v>3356.082511696385</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.718321525056267</v>
+        <v>21.08101984665918</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02431579797688656</v>
+        <v>5.475469950575495e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>O2 Flow (sccm)</t>
+          <t>Pressure (mTorr)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>294.9342358321036</v>
+        <v>681.9958605383139</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>11.75018220797055</v>
+        <v>4.283913825491864</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002036441722710586</v>
+        <v>0.04591836307120331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Anneal Condition Num × O2 Flow (sccm)</t>
+          <t>Anneal Temp (°C)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4825349759485696</v>
+        <v>17045.78512410306</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01922419712692172</v>
+        <v>107.0720202053284</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8907939963194552</v>
+        <v>3.441528942956249e-12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Pressure (mTorr)</t>
+          <t>Substrate Temp (°C)'):Q('O2 Flow (sccm)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66.88312428829539</v>
+        <v>1439.798331297608</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.664624182433647</v>
+        <v>9.04400207429034</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1146563374531817</v>
+        <v>0.0048553336724406</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Anneal Condition Num × Pressure (mTorr)</t>
+          <t>Power (W)'):Q('O2 Flow (sccm)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23.65182635877839</v>
+        <v>1636.748428734424</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.942288942763273</v>
+        <v>10.28113164378008</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3406343954748059</v>
+        <v>0.002869088757070998</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Anneal Temp (°C)</t>
+          <t>Residual</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17872.40986218387</v>
+        <v>5571.973688359693</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>712.0369454014107</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2.028335565072668e-20</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Anneal Condition Num × Anneal Temp (°C)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1035.956299795444</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>41.27250689547259</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8.314251789425394e-07</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Power (W) × Substrate Temp (°C)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1339.781174715107</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>53.37689223258949</v>
-      </c>
-      <c r="E13" t="n">
-        <v>9.285514852902966e-08</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Power (W) × O2 Flow (sccm)</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>200.7070284906017</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7.996169547869765</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.008903100274269283</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Power (W) × Pressure (mTorr)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>180.0727611775607</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7.174100180533839</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.01265062758059655</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Power (W) × Anneal Temp (°C)</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>81.78574540815336</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.258344721660448</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.08265536618269062</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Substrate Temp (°C) × O2 Flow (sccm)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>102.0370516151657</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>4.065156915607513</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.05421767421218069</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Substrate Temp (°C) × Pressure (mTorr)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3140.215006209983</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>125.1061898293</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.959270314298864e-11</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Substrate Temp (°C) × Anneal Temp (°C)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>7.446934705449674</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.2966859355375266</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.5906093219599611</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>O2 Flow (sccm) × Pressure (mTorr)</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>10.47893791648084</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.4174809666204866</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.5238593226133708</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>O2 Flow (sccm) × Anneal Temp (°C)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1009.845844954133</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>40.23226617518861</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.022673198870666e-06</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Pressure (mTorr) × Anneal Temp (°C)</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>345.8572915625466</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>13.77895713717195</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.0009862238692274635</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>Residual</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>652.6103166666667</v>
-      </c>
-      <c r="C23" t="n">
-        <v>26</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
